--- a/data/experience.xlsx
+++ b/data/experience.xlsx
@@ -1,34 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Makled\Desktop\portfolio, cv\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DDF75F-910F-4954-8C28-6F35E9DBEE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>StartDate</t>
+  </si>
+  <si>
+    <t>EndDate</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>LogoPath</t>
+  </si>
+  <si>
+    <t>02/2026</t>
+  </si>
+  <si>
+    <t>Digital Egypt Pioneers Initiative (DEPI) – Ministry of Communications and Information Technology</t>
+  </si>
+  <si>
+    <t>Cross-Platform Mobile App Developer Trainee</t>
+  </si>
+  <si>
+    <t>011/2025</t>
+  </si>
+  <si>
+    <t>07/2026</t>
+  </si>
+  <si>
+    <t>01/2026</t>
+  </si>
+  <si>
+    <t>Completed a 6-month project-based Flutter training program covering the full mobile application development lifecycle. Led the graduation project team and developed a production-ready cross-platform application using Flutter, Firebase, REST APIs, scalable architecture, local storage, and state management. Strengthened expertise in software engineering, Git/GitHub collaboration, unit testing, mobile security, Android &amp; iOS deployment, performance optimization, and professional communication.</t>
+  </si>
+  <si>
+    <t>National Telecommunication Institute (NTI) – Ministry of Communications and Information Technology</t>
+  </si>
+  <si>
+    <t>Mobile App Development Trainee</t>
+  </si>
+  <si>
+    <t>Completed 120+ hours of intensive Flutter training focused on Clean Architecture and scalable mobile application development. Built modular applications using Flutter, Dart, Firebase, REST APIs, and state management while improving debugging, performance optimization, and software engineering practices.</t>
+  </si>
+  <si>
+    <t>assets/logos/depi logo.png</t>
+  </si>
+  <si>
+    <t>assets/logos/nti logo.jpg</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +114,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,101 +418,79 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>StartDate</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>EndDate</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>LogoPath</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Digital Egypt Pioneers Initiative (DEPI) | Ministry of Communications and Information Technology</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cross-Platform Mobile App Development</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>07/2025</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Intensive training program in cross-platform mobile development using Flutter, focusing on real-world project implementation and deployment.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>National Telecommunication Institute (NTI)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cross-Platform Mobile App Development</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>02/2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>02/2026</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Advanced certification in Flutter development covering state management, architecture patterns, and production deployment.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
